--- a/exam_forms/004_gastric_physiology_knowledge_quiz--exam_forms.xlsx
+++ b/exam_forms/004_gastric_physiology_knowledge_quiz--exam_forms.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,12 +427,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -510,12 +510,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>first_page</t>
+          <t>page_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>what_is_gastric_cells</t>
+          <t>What are gastric cells?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -533,12 +533,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>what_are_hormones</t>
+          <t>page_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>gastric_hormones</t>
+          <t>What are hormones involved in gastric physiology?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -556,12 +556,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>mucosal_protection</t>
+          <t>page_3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>mucosal_protection</t>
+          <t>What is mucosal protection?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -579,12 +579,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>gastric_reflex</t>
+          <t>page_4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>gastric_reflex</t>
+          <t>How does gastric reflex work?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -602,12 +602,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>what_are_pepsinogens</t>
+          <t>page_5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>pepsinogens</t>
+          <t>What are pepsinogens?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -625,12 +625,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>what_are_gastrin</t>
+          <t>page_6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>gastrin</t>
+          <t>What are gastrin hormones?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -648,12 +648,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>what_is_mucous</t>
+          <t>page_7</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>mucous</t>
+          <t>What is the function of the pyloric sphincter?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -671,12 +671,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>what_is_parietal_cell</t>
+          <t>page_8</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>parietal_cell</t>
+          <t>What is the anatomy of the gastric mucosa?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -694,12 +694,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>what_are_gastric_anatomy</t>
+          <t>page_9</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>gastric_anatomy</t>
+          <t>What are the layers of the subepithelial?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -717,12 +717,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>what_are_mucous_membranes</t>
+          <t>page_10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>mucous_membranes</t>
+          <t>What is the function of gastric secretin?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -740,12 +740,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>what_is_gastric_muscularis</t>
+          <t>page_11</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>gastric_musclar</t>
+          <t>What is the structure of the mucous membranes?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -763,315 +763,16 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>what_is_submucosa</t>
+          <t>page_12</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>submucosa</t>
+          <t>What are the functions of the pylorus?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>what_is_subepithelial</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>subepithelial</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>what_is_gastric_secretin</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>gastric_secretin</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>what_is_mucin</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>mucin</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>what_are_gastric_mucosa</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>gastric_mucosa</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>what_is_pyloric_sphincter</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>pyloric_sphincter</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>what_is_gastric_pyloric_sphincter</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>gastric_pyloric_sphincter</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>what_are_gastric_pyloric_sphincter_function</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>pyloric_sphincter_function</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>what_are_gastric_mucous</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>mucous</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>what_are_pylorus</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>pylorus</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>what_are_gastric_pylorus</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>gastric_pylorus</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>what_is_gastric_secretin</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>gastric_secretin</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>what_is_mucous_membranes</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>mucous_membranes</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>what_is_pylorus_membranes</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>pylorus_membranes</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
